--- a/7_timetable.xlsx
+++ b/7_timetable.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hima71f\StudioProjects\oart2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09958EEC-1776-41CE-9E87-494E12DCC534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0228C91C-0FDB-4D7F-B108-D1949C1E9A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15252" yWindow="-108" windowWidth="15576" windowHeight="11784" xr2:uid="{EB897B52-549A-406B-97EF-94EC681855B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1 (2)" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$B$3:$F$47</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Sheet1 (2)'!$B$3:$F$47</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="31">
   <si>
     <t>時間</t>
     <rPh sb="0" eb="2">
@@ -151,10 +153,6 @@
     <rPh sb="2" eb="4">
       <t>ヒデキ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>「＊＊＊＊」</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -305,40 +303,6 @@
     </rPh>
     <rPh sb="37" eb="39">
       <t>ヒデキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>司会　大西麻衣、＊＊＊＊</t>
-    <rPh sb="0" eb="2">
-      <t>シカイ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>オオニシ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>マイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>①シーメンスヘルスケア株式会社
-「＊＊＊＊」</t>
-    <rPh sb="11" eb="13">
-      <t>カブシキ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>カイシャ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>②キヤノンメディカルシステムズ株式会社</t>
-    <rPh sb="15" eb="17">
-      <t>カブシキ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>カイシャ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -444,12 +408,84 @@
     <t>20+80+80+191+496+167+20</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>①シーメンスヘルスケア株式会社
+「クリニカルパスを変える可能性～フォトンカウンティングCTとAIの活用～]
+②キヤノンメディカルシステムズ株式会社
+「Aquilion Riseの挑戦 －マルチポジション撮影×先進技術による新たなポテンシャル－」
+司会　大西麻衣</t>
+    <rPh sb="11" eb="13">
+      <t>カブシキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カイシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">①シーメンスヘルスケア株式会社
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>「クリニカルパスを変える可能性～フォトンカウンティングCT
+とAIの活用～]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">
+②キヤノンメディカルシステムズ株式会社
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>「Aquilion Riseの挑戦 －マルチポジション撮影×先進技術による
+新たなポテンシャル－」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="メイリオ"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">
+司会　大西麻衣</t>
+    </r>
+    <rPh sb="11" eb="13">
+      <t>カブシキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カイシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -474,6 +510,20 @@
     </font>
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="メイリオ"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="メイリオ"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="メイリオ"/>
       <family val="3"/>
@@ -884,7 +934,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -912,12 +962,6 @@
     <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="20" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -972,12 +1016,27 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1056,15 +1115,6 @@
     <xf numFmtId="0" fontId="2" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="20" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -1092,11 +1142,17 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1125,6 +1181,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>511626</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>87089</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>470663</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>64159</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE056ADA-8533-ED23-CF92-802FF7A6530C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3341912" y="4343403"/>
+          <a:ext cx="3736380" cy="1479299"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1470,20 +1575,20 @@
     </row>
     <row r="2" spans="1:10" s="4" customFormat="1" ht="40.049999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" s="3"/>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="28" t="s">
-        <v>22</v>
+      <c r="F2" s="26" t="s">
+        <v>21</v>
       </c>
       <c r="G2" s="3"/>
     </row>
@@ -1499,7 +1604,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="66"/>
-      <c r="F3" s="13"/>
+      <c r="F3" s="11"/>
       <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
@@ -1508,7 +1613,7 @@
       <c r="C4" s="5"/>
       <c r="D4" s="65"/>
       <c r="E4" s="66"/>
-      <c r="F4" s="13"/>
+      <c r="F4" s="11"/>
       <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
@@ -1517,7 +1622,7 @@
       <c r="C5" s="6"/>
       <c r="D5" s="67"/>
       <c r="E5" s="68"/>
-      <c r="F5" s="13"/>
+      <c r="F5" s="11"/>
       <c r="G5" s="1"/>
     </row>
     <row r="6" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
@@ -1525,16 +1630,16 @@
       <c r="B6" s="60">
         <v>0.41666666666666702</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="9">
         <v>0.41666666666666669</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="13"/>
+      <c r="E6" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="11"/>
       <c r="G6" s="1"/>
     </row>
     <row r="7" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
@@ -1543,35 +1648,35 @@
       <c r="C7" s="5">
         <v>0.4236111111111111</v>
       </c>
-      <c r="D7" s="37" t="s">
+      <c r="D7" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="14"/>
+      <c r="E7" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="11"/>
       <c r="G7" s="1"/>
     </row>
     <row r="8" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="1"/>
       <c r="B8" s="61"/>
       <c r="C8" s="5"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="58" t="s">
-        <v>31</v>
-      </c>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="72"/>
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="1"/>
       <c r="B9" s="61"/>
       <c r="C9" s="5"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="58"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="29" t="s">
+        <v>27</v>
+      </c>
       <c r="G9" s="1"/>
-      <c r="J9" s="24">
+      <c r="J9" s="22">
         <f>7*60+30</f>
         <v>450</v>
       </c>
@@ -1580,21 +1685,21 @@
       <c r="A10" s="1"/>
       <c r="B10" s="61"/>
       <c r="C10" s="5"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="58"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="29"/>
       <c r="G10" s="1"/>
       <c r="I10" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="1"/>
       <c r="B11" s="62"/>
       <c r="C11" s="5"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="58"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="29"/>
       <c r="G11" s="1"/>
       <c r="I11" s="2">
         <f>33*49</f>
@@ -1607,33 +1712,33 @@
         <v>0.45833333333333298</v>
       </c>
       <c r="C12" s="5"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="58"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="29"/>
       <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="1"/>
       <c r="B13" s="61"/>
       <c r="C13" s="5"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="59"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="29"/>
       <c r="G13" s="1"/>
-      <c r="H13" s="25" t="s">
-        <v>15</v>
+      <c r="H13" s="23" t="s">
+        <v>14</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="1"/>
       <c r="B14" s="61"/>
       <c r="C14" s="6"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="15"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="30"/>
       <c r="G14" s="1"/>
       <c r="I14" s="2">
         <v>1054</v>
@@ -1645,20 +1750,20 @@
       <c r="C15" s="5">
         <v>0.47916666666666669</v>
       </c>
-      <c r="D15" s="31" t="s">
+      <c r="D15" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="32"/>
-      <c r="F15" s="16"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="14"/>
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="1"/>
       <c r="B16" s="61"/>
       <c r="C16" s="6"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="16"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="14"/>
       <c r="G16" s="1"/>
     </row>
     <row r="17" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
@@ -1667,13 +1772,13 @@
       <c r="C17" s="5">
         <v>0.49305555555555558</v>
       </c>
-      <c r="D17" s="40" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" s="69" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="16"/>
+      <c r="D17" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" s="14"/>
       <c r="G17" s="1"/>
     </row>
     <row r="18" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
@@ -1682,51 +1787,45 @@
         <v>0.5</v>
       </c>
       <c r="C18" s="5"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="70"/>
-      <c r="F18" s="16"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="14"/>
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="1"/>
       <c r="B19" s="61"/>
       <c r="C19" s="5"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="F19" s="16"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="14"/>
       <c r="G19" s="1"/>
     </row>
     <row r="20" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="1"/>
       <c r="B20" s="61"/>
       <c r="C20" s="5"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" s="16"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="14"/>
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="1"/>
       <c r="B21" s="61"/>
       <c r="C21" s="5"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="16"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="14"/>
       <c r="G21" s="1"/>
     </row>
     <row r="22" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="1"/>
       <c r="B22" s="61"/>
       <c r="C22" s="6"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F22" s="16"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="14"/>
       <c r="G22" s="1"/>
     </row>
     <row r="23" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
@@ -1735,11 +1834,11 @@
       <c r="C23" s="7">
         <v>0.53472222222222221</v>
       </c>
-      <c r="D23" s="31" t="s">
+      <c r="D23" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="E23" s="32"/>
-      <c r="F23" s="16"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="14"/>
       <c r="G23" s="1"/>
     </row>
     <row r="24" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
@@ -1748,9 +1847,9 @@
         <v>0.54166666666666696</v>
       </c>
       <c r="C24" s="6"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="16"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="14"/>
       <c r="G24" s="1"/>
     </row>
     <row r="25" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
@@ -1759,49 +1858,49 @@
       <c r="C25" s="5">
         <v>0.54861111111111116</v>
       </c>
-      <c r="D25" s="43" t="s">
+      <c r="D25" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="E25" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="F25" s="16"/>
+      <c r="E25" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="14"/>
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="1"/>
       <c r="B26" s="61"/>
       <c r="C26" s="5"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="16"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="14"/>
       <c r="G26" s="1"/>
     </row>
     <row r="27" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="1"/>
       <c r="B27" s="61"/>
       <c r="C27" s="5"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="44"/>
-      <c r="F27" s="16"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="14"/>
       <c r="G27" s="1"/>
     </row>
     <row r="28" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="1"/>
       <c r="B28" s="61"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="16"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="14"/>
       <c r="G28" s="1"/>
     </row>
     <row r="29" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="1"/>
       <c r="B29" s="62"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="44"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="16"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="14"/>
       <c r="G29" s="1"/>
     </row>
     <row r="30" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
@@ -1810,37 +1909,37 @@
         <v>0.58333333333333304</v>
       </c>
       <c r="C30" s="6"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="16"/>
+      <c r="D30" s="48"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="14"/>
       <c r="G30" s="1"/>
     </row>
     <row r="31" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="1"/>
       <c r="B31" s="61"/>
-      <c r="C31" s="11">
+      <c r="C31" s="9">
         <v>0.59027777777777779</v>
       </c>
-      <c r="D31" s="22" t="s">
+      <c r="D31" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="E31" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F31" s="16"/>
+      <c r="E31" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" s="14"/>
       <c r="G31" s="1"/>
     </row>
     <row r="32" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="1"/>
       <c r="B32" s="61"/>
-      <c r="C32" s="11">
+      <c r="C32" s="9">
         <v>0.59722222222222221</v>
       </c>
-      <c r="D32" s="35" t="s">
+      <c r="D32" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="E32" s="36"/>
-      <c r="F32" s="16"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="15"/>
       <c r="G32" s="1"/>
     </row>
     <row r="33" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
@@ -1849,31 +1948,33 @@
       <c r="C33" s="5">
         <v>0.60416666666666663</v>
       </c>
-      <c r="D33" s="46" t="s">
+      <c r="D33" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="F33" s="16"/>
+      <c r="E33" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="F33" s="28" t="s">
+        <v>26</v>
+      </c>
       <c r="G33" s="1"/>
     </row>
     <row r="34" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="1"/>
       <c r="B34" s="61"/>
       <c r="C34" s="5"/>
-      <c r="D34" s="47"/>
-      <c r="E34" s="53"/>
-      <c r="F34" s="16"/>
+      <c r="D34" s="50"/>
+      <c r="E34" s="56"/>
+      <c r="F34" s="29"/>
       <c r="G34" s="1"/>
     </row>
     <row r="35" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="1"/>
       <c r="B35" s="62"/>
       <c r="C35" s="5"/>
-      <c r="D35" s="47"/>
-      <c r="E35" s="53"/>
-      <c r="F35" s="17"/>
+      <c r="D35" s="50"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="29"/>
       <c r="G35" s="1"/>
     </row>
     <row r="36" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
@@ -1882,42 +1983,40 @@
         <v>0.625</v>
       </c>
       <c r="C36" s="5"/>
-      <c r="D36" s="47"/>
-      <c r="E36" s="53"/>
-      <c r="F36" s="57" t="s">
-        <v>30</v>
-      </c>
+      <c r="D36" s="50"/>
+      <c r="E36" s="56"/>
+      <c r="F36" s="29"/>
       <c r="G36" s="1"/>
     </row>
     <row r="37" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="1"/>
       <c r="B37" s="61"/>
       <c r="C37" s="5"/>
-      <c r="D37" s="47"/>
-      <c r="E37" s="53"/>
-      <c r="F37" s="58"/>
+      <c r="D37" s="50"/>
+      <c r="E37" s="56"/>
+      <c r="F37" s="29"/>
       <c r="G37" s="1"/>
     </row>
     <row r="38" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="1"/>
       <c r="B38" s="61"/>
       <c r="C38" s="6"/>
-      <c r="D38" s="48"/>
-      <c r="E38" s="54"/>
-      <c r="F38" s="58"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="30"/>
       <c r="G38" s="1"/>
     </row>
     <row r="39" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="1"/>
       <c r="B39" s="61"/>
-      <c r="C39" s="11">
+      <c r="C39" s="9">
         <v>0.64583333333333337</v>
       </c>
-      <c r="D39" s="35" t="s">
+      <c r="D39" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="E39" s="36"/>
-      <c r="F39" s="58"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="16"/>
       <c r="G39" s="1"/>
     </row>
     <row r="40" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
@@ -1926,22 +2025,22 @@
       <c r="C40" s="5">
         <v>0.65277777777777779</v>
       </c>
-      <c r="D40" s="49" t="s">
+      <c r="D40" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="E40" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="F40" s="58"/>
+      <c r="E40" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="F40" s="16"/>
       <c r="G40" s="1"/>
     </row>
     <row r="41" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="1"/>
       <c r="B41" s="62"/>
       <c r="C41" s="5"/>
-      <c r="D41" s="50"/>
-      <c r="E41" s="55"/>
-      <c r="F41" s="59"/>
+      <c r="D41" s="53"/>
+      <c r="E41" s="58"/>
+      <c r="F41" s="16"/>
       <c r="G41" s="1"/>
     </row>
     <row r="42" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
@@ -1950,66 +2049,66 @@
         <v>0.66666666666666696</v>
       </c>
       <c r="C42" s="5"/>
-      <c r="D42" s="50"/>
-      <c r="E42" s="55"/>
-      <c r="F42" s="29"/>
+      <c r="D42" s="53"/>
+      <c r="E42" s="58"/>
+      <c r="F42" s="16"/>
       <c r="G42" s="1"/>
     </row>
     <row r="43" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="1"/>
       <c r="B43" s="61"/>
       <c r="C43" s="5"/>
-      <c r="D43" s="50"/>
-      <c r="E43" s="55"/>
-      <c r="F43" s="18"/>
+      <c r="D43" s="53"/>
+      <c r="E43" s="58"/>
+      <c r="F43" s="16"/>
       <c r="G43" s="1"/>
     </row>
     <row r="44" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="1"/>
       <c r="B44" s="61"/>
       <c r="C44" s="5"/>
-      <c r="D44" s="50"/>
-      <c r="E44" s="55"/>
-      <c r="F44" s="18"/>
+      <c r="D44" s="53"/>
+      <c r="E44" s="58"/>
+      <c r="F44" s="16"/>
       <c r="G44" s="1"/>
     </row>
     <row r="45" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="1"/>
       <c r="B45" s="61"/>
       <c r="C45" s="6"/>
-      <c r="D45" s="51"/>
-      <c r="E45" s="56"/>
-      <c r="F45" s="18"/>
+      <c r="D45" s="54"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="16"/>
       <c r="G45" s="1"/>
     </row>
     <row r="46" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="1"/>
       <c r="B46" s="61"/>
-      <c r="C46" s="11">
+      <c r="C46" s="9">
         <v>0.69444444444444442</v>
       </c>
-      <c r="D46" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="E46" s="30" t="s">
+      <c r="D46" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="E46" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="F46" s="18"/>
+      <c r="F46" s="16"/>
       <c r="G46" s="1"/>
     </row>
     <row r="47" spans="1:7" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A47" s="1"/>
       <c r="B47" s="63"/>
-      <c r="C47" s="19">
+      <c r="C47" s="17">
         <v>0.70138888888888884</v>
       </c>
-      <c r="D47" s="20" t="s">
+      <c r="D47" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="E47" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="F47" s="21"/>
+      <c r="E47" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F47" s="19"/>
       <c r="G47" s="1"/>
     </row>
     <row r="48" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
@@ -2082,27 +2181,690 @@
     <mergeCell ref="B6:B11"/>
     <mergeCell ref="B12:B17"/>
     <mergeCell ref="D3:E5"/>
-    <mergeCell ref="F8:F13"/>
-    <mergeCell ref="E17:E18"/>
     <mergeCell ref="E7:E14"/>
     <mergeCell ref="D15:E16"/>
+    <mergeCell ref="F9:F14"/>
+    <mergeCell ref="E40:E45"/>
     <mergeCell ref="B36:B41"/>
     <mergeCell ref="B42:B47"/>
     <mergeCell ref="B18:B23"/>
     <mergeCell ref="B24:B29"/>
     <mergeCell ref="B30:B35"/>
-    <mergeCell ref="D40:D45"/>
-    <mergeCell ref="E25:E30"/>
-    <mergeCell ref="E33:E38"/>
-    <mergeCell ref="E40:E45"/>
-    <mergeCell ref="F36:F41"/>
-    <mergeCell ref="D23:E24"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D39:E39"/>
     <mergeCell ref="D7:D14"/>
     <mergeCell ref="D17:D22"/>
     <mergeCell ref="D25:D30"/>
     <mergeCell ref="D33:D38"/>
+    <mergeCell ref="D40:D45"/>
+    <mergeCell ref="F33:F38"/>
+    <mergeCell ref="E17:E22"/>
+    <mergeCell ref="D23:E24"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="E25:E30"/>
+    <mergeCell ref="E33:E38"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="79" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D29419C0-B5EC-4CD0-84D9-8596CFEBFF64}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J102"/>
+  <sheetFormatPr defaultRowHeight="21.6" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="2" style="2" customWidth="1"/>
+    <col min="2" max="3" width="8" style="2" customWidth="1"/>
+    <col min="4" max="4" width="19.09765625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="49.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="16.69921875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="2" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="8.796875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="1"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:10" s="4" customFormat="1" ht="40.049999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A2" s="3"/>
+      <c r="B2" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="1"/>
+      <c r="B3" s="61">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D3" s="65" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="66"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="1"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="1"/>
+      <c r="B5" s="62"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="1"/>
+      <c r="B6" s="60">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="C6" s="9">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="1"/>
+      <c r="B7" s="61"/>
+      <c r="C7" s="5">
+        <v>0.4236111111111111</v>
+      </c>
+      <c r="D7" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="12"/>
+      <c r="G7" s="1"/>
+    </row>
+    <row r="8" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="1"/>
+      <c r="B8" s="61"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="1"/>
+    </row>
+    <row r="9" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="1"/>
+      <c r="B9" s="61"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="1"/>
+      <c r="J9" s="22">
+        <f>7*60+30</f>
+        <v>450</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="1"/>
+      <c r="B10" s="61"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="1"/>
+      <c r="I10" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="1"/>
+      <c r="B11" s="62"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="1"/>
+      <c r="I11" s="2">
+        <f>33*49</f>
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="1"/>
+      <c r="B12" s="60">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="1"/>
+    </row>
+    <row r="13" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="1"/>
+      <c r="B13" s="61"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="1"/>
+      <c r="B14" s="61"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="1"/>
+      <c r="I14" s="2">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="1"/>
+      <c r="B15" s="61"/>
+      <c r="C15" s="5">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="35"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="1"/>
+    </row>
+    <row r="16" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="1"/>
+      <c r="B16" s="61"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="1:7" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="1"/>
+      <c r="B17" s="62"/>
+      <c r="C17" s="5">
+        <v>0.49305555555555558</v>
+      </c>
+      <c r="D17" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="69" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" s="14"/>
+      <c r="G17" s="1"/>
+    </row>
+    <row r="18" spans="1:7" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="1"/>
+      <c r="B18" s="60">
+        <v>0.5</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="1"/>
+    </row>
+    <row r="19" spans="1:7" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="1"/>
+      <c r="B19" s="61"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="1"/>
+    </row>
+    <row r="20" spans="1:7" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="1"/>
+      <c r="B20" s="61"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="1"/>
+    </row>
+    <row r="21" spans="1:7" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="1"/>
+      <c r="B21" s="61"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="1"/>
+    </row>
+    <row r="22" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="1"/>
+      <c r="B22" s="61"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="1"/>
+    </row>
+    <row r="23" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="1"/>
+      <c r="B23" s="62"/>
+      <c r="C23" s="7">
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="D23" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="35"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="1"/>
+    </row>
+    <row r="24" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="1"/>
+      <c r="B24" s="60">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="C24" s="6"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="1"/>
+      <c r="B25" s="61"/>
+      <c r="C25" s="5">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="D25" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="14"/>
+      <c r="G25" s="1"/>
+    </row>
+    <row r="26" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="1"/>
+      <c r="B26" s="61"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="1"/>
+    </row>
+    <row r="27" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="1"/>
+      <c r="B27" s="61"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="1"/>
+    </row>
+    <row r="28" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="1"/>
+      <c r="B28" s="61"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="1"/>
+    </row>
+    <row r="29" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="1"/>
+      <c r="B29" s="62"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="1"/>
+    </row>
+    <row r="30" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="1"/>
+      <c r="B30" s="60">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="C30" s="6"/>
+      <c r="D30" s="48"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="1"/>
+    </row>
+    <row r="31" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="1"/>
+      <c r="B31" s="61"/>
+      <c r="C31" s="9">
+        <v>0.59027777777777779</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" s="14"/>
+      <c r="G31" s="1"/>
+    </row>
+    <row r="32" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="1"/>
+      <c r="B32" s="61"/>
+      <c r="C32" s="9">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="D32" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="39"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="1"/>
+    </row>
+    <row r="33" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="1"/>
+      <c r="B33" s="61"/>
+      <c r="C33" s="5">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D33" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="F33" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="1"/>
+    </row>
+    <row r="34" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="1"/>
+      <c r="B34" s="61"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="50"/>
+      <c r="E34" s="56"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="1"/>
+    </row>
+    <row r="35" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="1"/>
+      <c r="B35" s="62"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="50"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="1"/>
+    </row>
+    <row r="36" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="1"/>
+      <c r="B36" s="60">
+        <v>0.625</v>
+      </c>
+      <c r="C36" s="5"/>
+      <c r="D36" s="50"/>
+      <c r="E36" s="56"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="1"/>
+    </row>
+    <row r="37" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="1"/>
+      <c r="B37" s="61"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="50"/>
+      <c r="E37" s="56"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="1"/>
+    </row>
+    <row r="38" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="1"/>
+      <c r="B38" s="61"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="1"/>
+    </row>
+    <row r="39" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="1"/>
+      <c r="B39" s="61"/>
+      <c r="C39" s="9">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D39" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="E39" s="39"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="1"/>
+    </row>
+    <row r="40" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="1"/>
+      <c r="B40" s="61"/>
+      <c r="C40" s="5">
+        <v>0.65277777777777779</v>
+      </c>
+      <c r="D40" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="F40" s="16"/>
+      <c r="G40" s="1"/>
+    </row>
+    <row r="41" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="1"/>
+      <c r="B41" s="62"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="53"/>
+      <c r="E41" s="58"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="1"/>
+    </row>
+    <row r="42" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="1"/>
+      <c r="B42" s="60">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="C42" s="5"/>
+      <c r="D42" s="53"/>
+      <c r="E42" s="58"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="1"/>
+    </row>
+    <row r="43" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="1"/>
+      <c r="B43" s="61"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="53"/>
+      <c r="E43" s="58"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="1"/>
+    </row>
+    <row r="44" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="1"/>
+      <c r="B44" s="61"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="53"/>
+      <c r="E44" s="58"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="1"/>
+    </row>
+    <row r="45" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="1"/>
+      <c r="B45" s="61"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="54"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="1"/>
+    </row>
+    <row r="46" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="1"/>
+      <c r="B46" s="61"/>
+      <c r="C46" s="9">
+        <v>0.69444444444444442</v>
+      </c>
+      <c r="D46" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="E46" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" s="16"/>
+      <c r="G46" s="1"/>
+    </row>
+    <row r="47" spans="1:7" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A47" s="1"/>
+      <c r="B47" s="63"/>
+      <c r="C47" s="17">
+        <v>0.70138888888888884</v>
+      </c>
+      <c r="D47" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F47" s="19"/>
+      <c r="G47" s="1"/>
+    </row>
+    <row r="48" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+    </row>
+    <row r="49" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="50" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="51" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="52" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="53" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="54" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="55" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="56" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="57" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="58" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="59" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="60" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="61" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="62" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="63" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="64" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="65" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="66" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="67" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="68" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="69" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="70" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="71" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="72" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="73" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="74" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="75" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="76" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="77" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="78" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="79" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="80" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="81" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="82" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="83" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="84" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="85" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="86" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="87" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="88" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="89" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="90" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="91" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="92" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="93" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="94" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="95" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="96" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="97" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="98" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="99" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="100" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="101" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="102" ht="10.35" customHeight="1" x14ac:dyDescent="0.45"/>
+  </sheetData>
+  <mergeCells count="26">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="D3:E5"/>
+    <mergeCell ref="B6:B11"/>
+    <mergeCell ref="D7:D14"/>
+    <mergeCell ref="E7:E14"/>
+    <mergeCell ref="F8:F13"/>
+    <mergeCell ref="B12:B17"/>
+    <mergeCell ref="D15:E16"/>
+    <mergeCell ref="D17:D22"/>
+    <mergeCell ref="E17:E22"/>
+    <mergeCell ref="B18:B23"/>
+    <mergeCell ref="D23:E24"/>
+    <mergeCell ref="B24:B29"/>
+    <mergeCell ref="D25:D30"/>
+    <mergeCell ref="E25:E30"/>
+    <mergeCell ref="B30:B35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D33:D38"/>
+    <mergeCell ref="E33:E38"/>
+    <mergeCell ref="F33:F38"/>
+    <mergeCell ref="B36:B41"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="D40:D45"/>
+    <mergeCell ref="E40:E45"/>
+    <mergeCell ref="B42:B47"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
